--- a/testik.xlsx
+++ b/testik.xlsx
@@ -424,7 +424,7 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>kolba/naveska</t>
+          <t>kolba_naveska</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
@@ -434,17 +434,17 @@
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>1_zamer/temp</t>
+          <t>zamer_temp_1</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t>2_zamer/temp</t>
+          <t>zamer_temp_2</t>
         </is>
       </c>
       <c r="G1" t="inlineStr">
         <is>
-          <t>3_zamer/temp</t>
+          <t>zamer_temp_3</t>
         </is>
       </c>
       <c r="H1" t="inlineStr">
@@ -454,32 +454,32 @@
       </c>
       <c r="I1" t="inlineStr">
         <is>
-          <t>gran_5-10_first</t>
+          <t>gran_5_10_first</t>
         </is>
       </c>
       <c r="J1" t="inlineStr">
         <is>
-          <t>gran_5-2_first</t>
+          <t>gran_5_2_first</t>
         </is>
       </c>
       <c r="K1" t="inlineStr">
         <is>
-          <t>gran_2-1_first</t>
+          <t>gran_2_1_first</t>
         </is>
       </c>
       <c r="L1" t="inlineStr">
         <is>
-          <t>gran_1-0,5_first</t>
+          <t>gran_1_0_5_first</t>
         </is>
       </c>
       <c r="M1" t="inlineStr">
         <is>
-          <t>gran_0,5-0,25_first</t>
+          <t>gran_0_5_0_25_first</t>
         </is>
       </c>
       <c r="N1" t="inlineStr">
         <is>
-          <t>gran_0,25-0,10_first</t>
+          <t>gran_0_25_0_10_first</t>
         </is>
       </c>
       <c r="O1" t="inlineStr">
@@ -541,15 +541,9 @@
       <c r="A3" t="n">
         <v>0</v>
       </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>26_09893</t>
-        </is>
-      </c>
       <c r="C3" t="n">
         <v>30.13</v>
       </c>
-      <c r="D3" t="inlineStr"/>
       <c r="E3" t="n">
         <v>20.5</v>
       </c>
@@ -559,13 +553,6 @@
       <c r="G3" t="n">
         <v>21</v>
       </c>
-      <c r="H3" t="inlineStr"/>
-      <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
       <c r="O3" t="n">
         <v>2</v>
       </c>
@@ -623,15 +610,9 @@
       <c r="A5" t="n">
         <v>1</v>
       </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>26_09897</t>
-        </is>
-      </c>
       <c r="C5" t="n">
         <v>30.23</v>
       </c>
-      <c r="D5" t="inlineStr"/>
       <c r="E5" t="n">
         <v>20.5</v>
       </c>
@@ -641,13 +622,6 @@
       <c r="G5" t="n">
         <v>21</v>
       </c>
-      <c r="H5" t="inlineStr"/>
-      <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr"/>
-      <c r="N5" t="inlineStr"/>
       <c r="O5" t="n">
         <v>2</v>
       </c>
@@ -705,15 +679,9 @@
       <c r="A7" t="n">
         <v>2</v>
       </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>26_09906</t>
-        </is>
-      </c>
       <c r="C7" t="n">
         <v>30.36</v>
       </c>
-      <c r="D7" t="inlineStr"/>
       <c r="E7" t="n">
         <v>20.5</v>
       </c>
@@ -723,13 +691,6 @@
       <c r="G7" t="n">
         <v>21</v>
       </c>
-      <c r="H7" t="inlineStr"/>
-      <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr"/>
-      <c r="N7" t="inlineStr"/>
       <c r="O7" t="n">
         <v>2</v>
       </c>
@@ -787,15 +748,9 @@
       <c r="A9" t="n">
         <v>3</v>
       </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>26_09919</t>
-        </is>
-      </c>
       <c r="C9" t="n">
         <v>30.12</v>
       </c>
-      <c r="D9" t="inlineStr"/>
       <c r="E9" t="n">
         <v>20.5</v>
       </c>
@@ -805,13 +760,6 @@
       <c r="G9" t="n">
         <v>21</v>
       </c>
-      <c r="H9" t="inlineStr"/>
-      <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr"/>
-      <c r="N9" t="inlineStr"/>
       <c r="O9" t="n">
         <v>2</v>
       </c>
@@ -869,15 +817,9 @@
       <c r="A11" t="n">
         <v>4</v>
       </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>26_09930</t>
-        </is>
-      </c>
       <c r="C11" t="n">
         <v>30.52</v>
       </c>
-      <c r="D11" t="inlineStr"/>
       <c r="E11" t="n">
         <v>20.5</v>
       </c>
@@ -887,13 +829,6 @@
       <c r="G11" t="n">
         <v>21</v>
       </c>
-      <c r="H11" t="inlineStr"/>
-      <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr"/>
-      <c r="N11" t="inlineStr"/>
       <c r="O11" t="n">
         <v>2</v>
       </c>
@@ -951,15 +886,9 @@
       <c r="A13" t="n">
         <v>5</v>
       </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>26_09932</t>
-        </is>
-      </c>
       <c r="C13" t="n">
         <v>30.75</v>
       </c>
-      <c r="D13" t="inlineStr"/>
       <c r="E13" t="n">
         <v>20.5</v>
       </c>
@@ -969,13 +898,6 @@
       <c r="G13" t="n">
         <v>21</v>
       </c>
-      <c r="H13" t="inlineStr"/>
-      <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
-      <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr"/>
-      <c r="N13" t="inlineStr"/>
       <c r="O13" t="n">
         <v>2</v>
       </c>
@@ -1033,15 +955,9 @@
       <c r="A15" t="n">
         <v>6</v>
       </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>26_09946</t>
-        </is>
-      </c>
       <c r="C15" t="n">
         <v>30.08</v>
       </c>
-      <c r="D15" t="inlineStr"/>
       <c r="E15" t="n">
         <v>20.5</v>
       </c>
@@ -1051,13 +967,6 @@
       <c r="G15" t="n">
         <v>21</v>
       </c>
-      <c r="H15" t="inlineStr"/>
-      <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr"/>
-      <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr"/>
-      <c r="N15" t="inlineStr"/>
       <c r="O15" t="n">
         <v>2</v>
       </c>
@@ -1115,15 +1024,9 @@
       <c r="A17" t="n">
         <v>7</v>
       </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>26_09953</t>
-        </is>
-      </c>
       <c r="C17" t="n">
         <v>30.72</v>
       </c>
-      <c r="D17" t="inlineStr"/>
       <c r="E17" t="n">
         <v>20.5</v>
       </c>
@@ -1133,13 +1036,6 @@
       <c r="G17" t="n">
         <v>21</v>
       </c>
-      <c r="H17" t="inlineStr"/>
-      <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr"/>
-      <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
-      <c r="M17" t="inlineStr"/>
-      <c r="N17" t="inlineStr"/>
       <c r="O17" t="n">
         <v>2</v>
       </c>
@@ -1197,15 +1093,9 @@
       <c r="A19" t="n">
         <v>8</v>
       </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>26_10438</t>
-        </is>
-      </c>
       <c r="C19" t="n">
         <v>30.38</v>
       </c>
-      <c r="D19" t="inlineStr"/>
       <c r="E19" t="n">
         <v>20.5</v>
       </c>
@@ -1215,13 +1105,6 @@
       <c r="G19" t="n">
         <v>21</v>
       </c>
-      <c r="H19" t="inlineStr"/>
-      <c r="I19" t="inlineStr"/>
-      <c r="J19" t="inlineStr"/>
-      <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
-      <c r="M19" t="inlineStr"/>
-      <c r="N19" t="inlineStr"/>
       <c r="O19" t="n">
         <v>2</v>
       </c>
@@ -1279,15 +1162,9 @@
       <c r="A21" t="n">
         <v>9</v>
       </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>26_10439</t>
-        </is>
-      </c>
       <c r="C21" t="n">
         <v>30.14</v>
       </c>
-      <c r="D21" t="inlineStr"/>
       <c r="E21" t="n">
         <v>20</v>
       </c>
@@ -1297,13 +1174,6 @@
       <c r="G21" t="n">
         <v>21</v>
       </c>
-      <c r="H21" t="inlineStr"/>
-      <c r="I21" t="inlineStr"/>
-      <c r="J21" t="inlineStr"/>
-      <c r="K21" t="inlineStr"/>
-      <c r="L21" t="inlineStr"/>
-      <c r="M21" t="inlineStr"/>
-      <c r="N21" t="inlineStr"/>
       <c r="O21" t="n">
         <v>2</v>
       </c>
@@ -1361,15 +1231,9 @@
       <c r="A23" t="n">
         <v>10</v>
       </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>26_10440</t>
-        </is>
-      </c>
       <c r="C23" t="n">
         <v>30.82</v>
       </c>
-      <c r="D23" t="inlineStr"/>
       <c r="E23" t="n">
         <v>20</v>
       </c>
@@ -1379,13 +1243,6 @@
       <c r="G23" t="n">
         <v>21</v>
       </c>
-      <c r="H23" t="inlineStr"/>
-      <c r="I23" t="inlineStr"/>
-      <c r="J23" t="inlineStr"/>
-      <c r="K23" t="inlineStr"/>
-      <c r="L23" t="inlineStr"/>
-      <c r="M23" t="inlineStr"/>
-      <c r="N23" t="inlineStr"/>
       <c r="O23" t="n">
         <v>2</v>
       </c>
@@ -1443,15 +1300,9 @@
       <c r="A25" t="n">
         <v>11</v>
       </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>26_10441</t>
-        </is>
-      </c>
       <c r="C25" t="n">
         <v>30.24</v>
       </c>
-      <c r="D25" t="inlineStr"/>
       <c r="E25" t="n">
         <v>20</v>
       </c>
@@ -1461,13 +1312,6 @@
       <c r="G25" t="n">
         <v>21</v>
       </c>
-      <c r="H25" t="inlineStr"/>
-      <c r="I25" t="inlineStr"/>
-      <c r="J25" t="inlineStr"/>
-      <c r="K25" t="inlineStr"/>
-      <c r="L25" t="inlineStr"/>
-      <c r="M25" t="inlineStr"/>
-      <c r="N25" t="inlineStr"/>
       <c r="O25" t="n">
         <v>2</v>
       </c>
@@ -1525,15 +1369,9 @@
       <c r="A27" t="n">
         <v>12</v>
       </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>26_10442</t>
-        </is>
-      </c>
       <c r="C27" t="n">
         <v>30.01</v>
       </c>
-      <c r="D27" t="inlineStr"/>
       <c r="E27" t="n">
         <v>20</v>
       </c>
@@ -1543,13 +1381,6 @@
       <c r="G27" t="n">
         <v>21</v>
       </c>
-      <c r="H27" t="inlineStr"/>
-      <c r="I27" t="inlineStr"/>
-      <c r="J27" t="inlineStr"/>
-      <c r="K27" t="inlineStr"/>
-      <c r="L27" t="inlineStr"/>
-      <c r="M27" t="inlineStr"/>
-      <c r="N27" t="inlineStr"/>
       <c r="O27" t="n">
         <v>2</v>
       </c>
@@ -1607,15 +1438,9 @@
       <c r="A29" t="n">
         <v>13</v>
       </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>26_10443</t>
-        </is>
-      </c>
       <c r="C29" t="n">
         <v>30.54</v>
       </c>
-      <c r="D29" t="inlineStr"/>
       <c r="E29" t="n">
         <v>20</v>
       </c>
@@ -1625,13 +1450,6 @@
       <c r="G29" t="n">
         <v>21</v>
       </c>
-      <c r="H29" t="inlineStr"/>
-      <c r="I29" t="inlineStr"/>
-      <c r="J29" t="inlineStr"/>
-      <c r="K29" t="inlineStr"/>
-      <c r="L29" t="inlineStr"/>
-      <c r="M29" t="inlineStr"/>
-      <c r="N29" t="inlineStr"/>
       <c r="O29" t="n">
         <v>2</v>
       </c>
@@ -1689,15 +1507,9 @@
       <c r="A31" t="n">
         <v>14</v>
       </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>26_10444</t>
-        </is>
-      </c>
       <c r="C31" t="n">
         <v>30.09</v>
       </c>
-      <c r="D31" t="inlineStr"/>
       <c r="E31" t="n">
         <v>20</v>
       </c>
@@ -1707,13 +1519,6 @@
       <c r="G31" t="n">
         <v>21</v>
       </c>
-      <c r="H31" t="inlineStr"/>
-      <c r="I31" t="inlineStr"/>
-      <c r="J31" t="inlineStr"/>
-      <c r="K31" t="inlineStr"/>
-      <c r="L31" t="inlineStr"/>
-      <c r="M31" t="inlineStr"/>
-      <c r="N31" t="inlineStr"/>
       <c r="O31" t="n">
         <v>2</v>
       </c>
@@ -1771,15 +1576,9 @@
       <c r="A33" t="n">
         <v>15</v>
       </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>26_10445</t>
-        </is>
-      </c>
       <c r="C33" t="n">
         <v>30.01</v>
       </c>
-      <c r="D33" t="inlineStr"/>
       <c r="E33" t="n">
         <v>20</v>
       </c>
@@ -1789,13 +1588,6 @@
       <c r="G33" t="n">
         <v>21</v>
       </c>
-      <c r="H33" t="inlineStr"/>
-      <c r="I33" t="inlineStr"/>
-      <c r="J33" t="inlineStr"/>
-      <c r="K33" t="inlineStr"/>
-      <c r="L33" t="inlineStr"/>
-      <c r="M33" t="inlineStr"/>
-      <c r="N33" t="inlineStr"/>
       <c r="O33" t="n">
         <v>2</v>
       </c>
@@ -1853,15 +1645,9 @@
       <c r="A35" t="n">
         <v>16</v>
       </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>26_10446</t>
-        </is>
-      </c>
       <c r="C35" t="n">
         <v>30.48</v>
       </c>
-      <c r="D35" t="inlineStr"/>
       <c r="E35" t="n">
         <v>20</v>
       </c>
@@ -1871,13 +1657,6 @@
       <c r="G35" t="n">
         <v>21</v>
       </c>
-      <c r="H35" t="inlineStr"/>
-      <c r="I35" t="inlineStr"/>
-      <c r="J35" t="inlineStr"/>
-      <c r="K35" t="inlineStr"/>
-      <c r="L35" t="inlineStr"/>
-      <c r="M35" t="inlineStr"/>
-      <c r="N35" t="inlineStr"/>
       <c r="O35" t="n">
         <v>2</v>
       </c>
@@ -1935,15 +1714,9 @@
       <c r="A37" t="n">
         <v>17</v>
       </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>26_10447</t>
-        </is>
-      </c>
       <c r="C37" t="n">
         <v>30.43</v>
       </c>
-      <c r="D37" t="inlineStr"/>
       <c r="E37" t="n">
         <v>20</v>
       </c>
@@ -1953,13 +1726,6 @@
       <c r="G37" t="n">
         <v>21</v>
       </c>
-      <c r="H37" t="inlineStr"/>
-      <c r="I37" t="inlineStr"/>
-      <c r="J37" t="inlineStr"/>
-      <c r="K37" t="inlineStr"/>
-      <c r="L37" t="inlineStr"/>
-      <c r="M37" t="inlineStr"/>
-      <c r="N37" t="inlineStr"/>
       <c r="O37" t="n">
         <v>2</v>
       </c>
@@ -2017,15 +1783,9 @@
       <c r="A39" t="n">
         <v>18</v>
       </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>26_10448</t>
-        </is>
-      </c>
       <c r="C39" t="n">
         <v>30.18</v>
       </c>
-      <c r="D39" t="inlineStr"/>
       <c r="E39" t="n">
         <v>20</v>
       </c>
@@ -2035,13 +1795,6 @@
       <c r="G39" t="n">
         <v>21</v>
       </c>
-      <c r="H39" t="inlineStr"/>
-      <c r="I39" t="inlineStr"/>
-      <c r="J39" t="inlineStr"/>
-      <c r="K39" t="inlineStr"/>
-      <c r="L39" t="inlineStr"/>
-      <c r="M39" t="inlineStr"/>
-      <c r="N39" t="inlineStr"/>
       <c r="O39" t="n">
         <v>2</v>
       </c>
@@ -2099,15 +1852,9 @@
       <c r="A41" t="n">
         <v>19</v>
       </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>26_10449</t>
-        </is>
-      </c>
       <c r="C41" t="n">
         <v>30.19</v>
       </c>
-      <c r="D41" t="inlineStr"/>
       <c r="E41" t="n">
         <v>20</v>
       </c>
@@ -2117,13 +1864,6 @@
       <c r="G41" t="n">
         <v>21</v>
       </c>
-      <c r="H41" t="inlineStr"/>
-      <c r="I41" t="inlineStr"/>
-      <c r="J41" t="inlineStr"/>
-      <c r="K41" t="inlineStr"/>
-      <c r="L41" t="inlineStr"/>
-      <c r="M41" t="inlineStr"/>
-      <c r="N41" t="inlineStr"/>
       <c r="O41" t="n">
         <v>2</v>
       </c>
@@ -2181,15 +1921,9 @@
       <c r="A43" t="n">
         <v>20</v>
       </c>
-      <c r="B43" t="inlineStr">
-        <is>
-          <t>26_10450</t>
-        </is>
-      </c>
       <c r="C43" t="n">
         <v>30.54</v>
       </c>
-      <c r="D43" t="inlineStr"/>
       <c r="E43" t="n">
         <v>20</v>
       </c>
@@ -2199,13 +1933,6 @@
       <c r="G43" t="n">
         <v>21</v>
       </c>
-      <c r="H43" t="inlineStr"/>
-      <c r="I43" t="inlineStr"/>
-      <c r="J43" t="inlineStr"/>
-      <c r="K43" t="inlineStr"/>
-      <c r="L43" t="inlineStr"/>
-      <c r="M43" t="inlineStr"/>
-      <c r="N43" t="inlineStr"/>
       <c r="O43" t="n">
         <v>2</v>
       </c>
@@ -2263,15 +1990,9 @@
       <c r="A45" t="n">
         <v>21</v>
       </c>
-      <c r="B45" t="inlineStr">
-        <is>
-          <t>26_10452</t>
-        </is>
-      </c>
       <c r="C45" t="n">
         <v>31.17</v>
       </c>
-      <c r="D45" t="inlineStr"/>
       <c r="E45" t="n">
         <v>20</v>
       </c>
@@ -2281,13 +2002,6 @@
       <c r="G45" t="n">
         <v>21</v>
       </c>
-      <c r="H45" t="inlineStr"/>
-      <c r="I45" t="inlineStr"/>
-      <c r="J45" t="inlineStr"/>
-      <c r="K45" t="inlineStr"/>
-      <c r="L45" t="inlineStr"/>
-      <c r="M45" t="inlineStr"/>
-      <c r="N45" t="inlineStr"/>
       <c r="O45" t="n">
         <v>2</v>
       </c>
@@ -2345,15 +2059,9 @@
       <c r="A47" t="n">
         <v>22</v>
       </c>
-      <c r="B47" t="inlineStr">
-        <is>
-          <t>26_10453</t>
-        </is>
-      </c>
       <c r="C47" t="n">
         <v>31.35</v>
       </c>
-      <c r="D47" t="inlineStr"/>
       <c r="E47" t="n">
         <v>20</v>
       </c>
@@ -2363,13 +2071,6 @@
       <c r="G47" t="n">
         <v>21</v>
       </c>
-      <c r="H47" t="inlineStr"/>
-      <c r="I47" t="inlineStr"/>
-      <c r="J47" t="inlineStr"/>
-      <c r="K47" t="inlineStr"/>
-      <c r="L47" t="inlineStr"/>
-      <c r="M47" t="inlineStr"/>
-      <c r="N47" t="inlineStr"/>
       <c r="O47" t="n">
         <v>2</v>
       </c>
@@ -2427,15 +2128,9 @@
       <c r="A49" t="n">
         <v>23</v>
       </c>
-      <c r="B49" t="inlineStr">
-        <is>
-          <t>26_10454</t>
-        </is>
-      </c>
       <c r="C49" t="n">
         <v>30.6</v>
       </c>
-      <c r="D49" t="inlineStr"/>
       <c r="E49" t="n">
         <v>20</v>
       </c>
@@ -2445,13 +2140,6 @@
       <c r="G49" t="n">
         <v>21</v>
       </c>
-      <c r="H49" t="inlineStr"/>
-      <c r="I49" t="inlineStr"/>
-      <c r="J49" t="inlineStr"/>
-      <c r="K49" t="inlineStr"/>
-      <c r="L49" t="inlineStr"/>
-      <c r="M49" t="inlineStr"/>
-      <c r="N49" t="inlineStr"/>
       <c r="O49" t="n">
         <v>2</v>
       </c>
@@ -2509,15 +2197,9 @@
       <c r="A51" t="n">
         <v>24</v>
       </c>
-      <c r="B51" t="inlineStr">
-        <is>
-          <t>26_10455</t>
-        </is>
-      </c>
       <c r="C51" t="n">
         <v>30.24</v>
       </c>
-      <c r="D51" t="inlineStr"/>
       <c r="E51" t="n">
         <v>20.5</v>
       </c>
@@ -2527,13 +2209,6 @@
       <c r="G51" t="n">
         <v>21</v>
       </c>
-      <c r="H51" t="inlineStr"/>
-      <c r="I51" t="inlineStr"/>
-      <c r="J51" t="inlineStr"/>
-      <c r="K51" t="inlineStr"/>
-      <c r="L51" t="inlineStr"/>
-      <c r="M51" t="inlineStr"/>
-      <c r="N51" t="inlineStr"/>
       <c r="O51" t="n">
         <v>2</v>
       </c>
@@ -2591,15 +2266,9 @@
       <c r="A53" t="n">
         <v>25</v>
       </c>
-      <c r="B53" t="inlineStr">
-        <is>
-          <t>26_10456</t>
-        </is>
-      </c>
       <c r="C53" t="n">
         <v>30.29</v>
       </c>
-      <c r="D53" t="inlineStr"/>
       <c r="E53" t="n">
         <v>20</v>
       </c>
@@ -2609,13 +2278,6 @@
       <c r="G53" t="n">
         <v>21</v>
       </c>
-      <c r="H53" t="inlineStr"/>
-      <c r="I53" t="inlineStr"/>
-      <c r="J53" t="inlineStr"/>
-      <c r="K53" t="inlineStr"/>
-      <c r="L53" t="inlineStr"/>
-      <c r="M53" t="inlineStr"/>
-      <c r="N53" t="inlineStr"/>
       <c r="O53" t="n">
         <v>2</v>
       </c>
@@ -2673,15 +2335,9 @@
       <c r="A55" t="n">
         <v>26</v>
       </c>
-      <c r="B55" t="inlineStr">
-        <is>
-          <t>26_10458</t>
-        </is>
-      </c>
       <c r="C55" t="n">
         <v>30.05</v>
       </c>
-      <c r="D55" t="inlineStr"/>
       <c r="E55" t="n">
         <v>20</v>
       </c>
@@ -2691,13 +2347,6 @@
       <c r="G55" t="n">
         <v>21</v>
       </c>
-      <c r="H55" t="inlineStr"/>
-      <c r="I55" t="inlineStr"/>
-      <c r="J55" t="inlineStr"/>
-      <c r="K55" t="inlineStr"/>
-      <c r="L55" t="inlineStr"/>
-      <c r="M55" t="inlineStr"/>
-      <c r="N55" t="inlineStr"/>
       <c r="O55" t="n">
         <v>2</v>
       </c>
@@ -2755,15 +2404,9 @@
       <c r="A57" t="n">
         <v>27</v>
       </c>
-      <c r="B57" t="inlineStr">
-        <is>
-          <t>26_10459</t>
-        </is>
-      </c>
       <c r="C57" t="n">
         <v>30.14</v>
       </c>
-      <c r="D57" t="inlineStr"/>
       <c r="E57" t="n">
         <v>20</v>
       </c>
@@ -2773,13 +2416,6 @@
       <c r="G57" t="n">
         <v>21</v>
       </c>
-      <c r="H57" t="inlineStr"/>
-      <c r="I57" t="inlineStr"/>
-      <c r="J57" t="inlineStr"/>
-      <c r="K57" t="inlineStr"/>
-      <c r="L57" t="inlineStr"/>
-      <c r="M57" t="inlineStr"/>
-      <c r="N57" t="inlineStr"/>
       <c r="O57" t="n">
         <v>2</v>
       </c>
@@ -2837,15 +2473,9 @@
       <c r="A59" t="n">
         <v>28</v>
       </c>
-      <c r="B59" t="inlineStr">
-        <is>
-          <t>26_10460</t>
-        </is>
-      </c>
       <c r="C59" t="n">
         <v>30.55</v>
       </c>
-      <c r="D59" t="inlineStr"/>
       <c r="E59" t="n">
         <v>20</v>
       </c>
@@ -2855,13 +2485,6 @@
       <c r="G59" t="n">
         <v>21</v>
       </c>
-      <c r="H59" t="inlineStr"/>
-      <c r="I59" t="inlineStr"/>
-      <c r="J59" t="inlineStr"/>
-      <c r="K59" t="inlineStr"/>
-      <c r="L59" t="inlineStr"/>
-      <c r="M59" t="inlineStr"/>
-      <c r="N59" t="inlineStr"/>
       <c r="O59" t="n">
         <v>2</v>
       </c>
@@ -2919,15 +2542,9 @@
       <c r="A61" t="n">
         <v>29</v>
       </c>
-      <c r="B61" t="inlineStr">
-        <is>
-          <t>26_10461</t>
-        </is>
-      </c>
       <c r="C61" t="n">
         <v>30.64</v>
       </c>
-      <c r="D61" t="inlineStr"/>
       <c r="E61" t="n">
         <v>20</v>
       </c>
@@ -2937,13 +2554,6 @@
       <c r="G61" t="n">
         <v>21</v>
       </c>
-      <c r="H61" t="inlineStr"/>
-      <c r="I61" t="inlineStr"/>
-      <c r="J61" t="inlineStr"/>
-      <c r="K61" t="inlineStr"/>
-      <c r="L61" t="inlineStr"/>
-      <c r="M61" t="inlineStr"/>
-      <c r="N61" t="inlineStr"/>
       <c r="O61" t="n">
         <v>2</v>
       </c>
@@ -3001,15 +2611,9 @@
       <c r="A63" t="n">
         <v>30</v>
       </c>
-      <c r="B63" t="inlineStr">
-        <is>
-          <t>26_10462</t>
-        </is>
-      </c>
       <c r="C63" t="n">
         <v>30.12</v>
       </c>
-      <c r="D63" t="inlineStr"/>
       <c r="E63" t="n">
         <v>20</v>
       </c>
@@ -3019,13 +2623,6 @@
       <c r="G63" t="n">
         <v>21</v>
       </c>
-      <c r="H63" t="inlineStr"/>
-      <c r="I63" t="inlineStr"/>
-      <c r="J63" t="inlineStr"/>
-      <c r="K63" t="inlineStr"/>
-      <c r="L63" t="inlineStr"/>
-      <c r="M63" t="inlineStr"/>
-      <c r="N63" t="inlineStr"/>
       <c r="O63" t="n">
         <v>2</v>
       </c>
@@ -3083,15 +2680,9 @@
       <c r="A65" t="n">
         <v>31</v>
       </c>
-      <c r="B65" t="inlineStr">
-        <is>
-          <t>26_10464</t>
-        </is>
-      </c>
       <c r="C65" t="n">
         <v>30.3</v>
       </c>
-      <c r="D65" t="inlineStr"/>
       <c r="E65" t="n">
         <v>20</v>
       </c>
@@ -3101,13 +2692,6 @@
       <c r="G65" t="n">
         <v>21</v>
       </c>
-      <c r="H65" t="inlineStr"/>
-      <c r="I65" t="inlineStr"/>
-      <c r="J65" t="inlineStr"/>
-      <c r="K65" t="inlineStr"/>
-      <c r="L65" t="inlineStr"/>
-      <c r="M65" t="inlineStr"/>
-      <c r="N65" t="inlineStr"/>
       <c r="O65" t="n">
         <v>2</v>
       </c>
@@ -3165,15 +2749,9 @@
       <c r="A67" t="n">
         <v>32</v>
       </c>
-      <c r="B67" t="inlineStr">
-        <is>
-          <t>26_10465</t>
-        </is>
-      </c>
       <c r="C67" t="n">
         <v>30.31</v>
       </c>
-      <c r="D67" t="inlineStr"/>
       <c r="E67" t="n">
         <v>20</v>
       </c>
@@ -3183,13 +2761,6 @@
       <c r="G67" t="n">
         <v>21</v>
       </c>
-      <c r="H67" t="inlineStr"/>
-      <c r="I67" t="inlineStr"/>
-      <c r="J67" t="inlineStr"/>
-      <c r="K67" t="inlineStr"/>
-      <c r="L67" t="inlineStr"/>
-      <c r="M67" t="inlineStr"/>
-      <c r="N67" t="inlineStr"/>
       <c r="O67" t="n">
         <v>2</v>
       </c>
@@ -3247,15 +2818,9 @@
       <c r="A69" t="n">
         <v>33</v>
       </c>
-      <c r="B69" t="inlineStr">
-        <is>
-          <t>26_10466</t>
-        </is>
-      </c>
       <c r="C69" t="n">
         <v>31.94</v>
       </c>
-      <c r="D69" t="inlineStr"/>
       <c r="E69" t="n">
         <v>20.5</v>
       </c>
@@ -3265,13 +2830,6 @@
       <c r="G69" t="n">
         <v>21</v>
       </c>
-      <c r="H69" t="inlineStr"/>
-      <c r="I69" t="inlineStr"/>
-      <c r="J69" t="inlineStr"/>
-      <c r="K69" t="inlineStr"/>
-      <c r="L69" t="inlineStr"/>
-      <c r="M69" t="inlineStr"/>
-      <c r="N69" t="inlineStr"/>
       <c r="O69" t="n">
         <v>2</v>
       </c>
@@ -3329,15 +2887,9 @@
       <c r="A71" t="n">
         <v>34</v>
       </c>
-      <c r="B71" t="inlineStr">
-        <is>
-          <t>26_10467</t>
-        </is>
-      </c>
       <c r="C71" t="n">
         <v>30.65</v>
       </c>
-      <c r="D71" t="inlineStr"/>
       <c r="E71" t="n">
         <v>20</v>
       </c>
@@ -3347,13 +2899,6 @@
       <c r="G71" t="n">
         <v>21</v>
       </c>
-      <c r="H71" t="inlineStr"/>
-      <c r="I71" t="inlineStr"/>
-      <c r="J71" t="inlineStr"/>
-      <c r="K71" t="inlineStr"/>
-      <c r="L71" t="inlineStr"/>
-      <c r="M71" t="inlineStr"/>
-      <c r="N71" t="inlineStr"/>
       <c r="O71" t="n">
         <v>2</v>
       </c>
@@ -3411,15 +2956,9 @@
       <c r="A73" t="n">
         <v>35</v>
       </c>
-      <c r="B73" t="inlineStr">
-        <is>
-          <t>26_10468</t>
-        </is>
-      </c>
       <c r="C73" t="n">
         <v>30.82</v>
       </c>
-      <c r="D73" t="inlineStr"/>
       <c r="E73" t="n">
         <v>20.5</v>
       </c>
@@ -3429,13 +2968,6 @@
       <c r="G73" t="n">
         <v>21</v>
       </c>
-      <c r="H73" t="inlineStr"/>
-      <c r="I73" t="inlineStr"/>
-      <c r="J73" t="inlineStr"/>
-      <c r="K73" t="inlineStr"/>
-      <c r="L73" t="inlineStr"/>
-      <c r="M73" t="inlineStr"/>
-      <c r="N73" t="inlineStr"/>
       <c r="O73" t="n">
         <v>2</v>
       </c>
@@ -3493,15 +3025,9 @@
       <c r="A75" t="n">
         <v>36</v>
       </c>
-      <c r="B75" t="inlineStr">
-        <is>
-          <t>26_10471</t>
-        </is>
-      </c>
       <c r="C75" t="n">
         <v>30.21</v>
       </c>
-      <c r="D75" t="inlineStr"/>
       <c r="E75" t="n">
         <v>20.5</v>
       </c>
@@ -3511,13 +3037,6 @@
       <c r="G75" t="n">
         <v>21</v>
       </c>
-      <c r="H75" t="inlineStr"/>
-      <c r="I75" t="inlineStr"/>
-      <c r="J75" t="inlineStr"/>
-      <c r="K75" t="inlineStr"/>
-      <c r="L75" t="inlineStr"/>
-      <c r="M75" t="inlineStr"/>
-      <c r="N75" t="inlineStr"/>
       <c r="O75" t="n">
         <v>2</v>
       </c>
@@ -3575,15 +3094,9 @@
       <c r="A77" t="n">
         <v>37</v>
       </c>
-      <c r="B77" t="inlineStr">
-        <is>
-          <t>26_10472</t>
-        </is>
-      </c>
       <c r="C77" t="n">
         <v>31.08</v>
       </c>
-      <c r="D77" t="inlineStr"/>
       <c r="E77" t="n">
         <v>20.5</v>
       </c>
@@ -3593,13 +3106,6 @@
       <c r="G77" t="n">
         <v>21</v>
       </c>
-      <c r="H77" t="inlineStr"/>
-      <c r="I77" t="inlineStr"/>
-      <c r="J77" t="inlineStr"/>
-      <c r="K77" t="inlineStr"/>
-      <c r="L77" t="inlineStr"/>
-      <c r="M77" t="inlineStr"/>
-      <c r="N77" t="inlineStr"/>
       <c r="O77" t="n">
         <v>2</v>
       </c>
@@ -3657,15 +3163,9 @@
       <c r="A79" t="n">
         <v>38</v>
       </c>
-      <c r="B79" t="inlineStr">
-        <is>
-          <t>26_10473</t>
-        </is>
-      </c>
       <c r="C79" t="n">
         <v>30.14</v>
       </c>
-      <c r="D79" t="inlineStr"/>
       <c r="E79" t="n">
         <v>20.5</v>
       </c>
@@ -3675,13 +3175,6 @@
       <c r="G79" t="n">
         <v>21</v>
       </c>
-      <c r="H79" t="inlineStr"/>
-      <c r="I79" t="inlineStr"/>
-      <c r="J79" t="inlineStr"/>
-      <c r="K79" t="inlineStr"/>
-      <c r="L79" t="inlineStr"/>
-      <c r="M79" t="inlineStr"/>
-      <c r="N79" t="inlineStr"/>
       <c r="O79" t="n">
         <v>2</v>
       </c>
@@ -3739,15 +3232,9 @@
       <c r="A81" t="n">
         <v>39</v>
       </c>
-      <c r="B81" t="inlineStr">
-        <is>
-          <t>26_10474</t>
-        </is>
-      </c>
       <c r="C81" t="n">
         <v>30.4</v>
       </c>
-      <c r="D81" t="inlineStr"/>
       <c r="E81" t="n">
         <v>20.5</v>
       </c>
@@ -3757,13 +3244,6 @@
       <c r="G81" t="n">
         <v>21</v>
       </c>
-      <c r="H81" t="inlineStr"/>
-      <c r="I81" t="inlineStr"/>
-      <c r="J81" t="inlineStr"/>
-      <c r="K81" t="inlineStr"/>
-      <c r="L81" t="inlineStr"/>
-      <c r="M81" t="inlineStr"/>
-      <c r="N81" t="inlineStr"/>
       <c r="O81" t="n">
         <v>2</v>
       </c>
@@ -3821,15 +3301,9 @@
       <c r="A83" t="n">
         <v>40</v>
       </c>
-      <c r="B83" t="inlineStr">
-        <is>
-          <t>26_10475</t>
-        </is>
-      </c>
       <c r="C83" t="n">
         <v>31.43</v>
       </c>
-      <c r="D83" t="inlineStr"/>
       <c r="E83" t="n">
         <v>20.5</v>
       </c>
@@ -3839,13 +3313,6 @@
       <c r="G83" t="n">
         <v>21</v>
       </c>
-      <c r="H83" t="inlineStr"/>
-      <c r="I83" t="inlineStr"/>
-      <c r="J83" t="inlineStr"/>
-      <c r="K83" t="inlineStr"/>
-      <c r="L83" t="inlineStr"/>
-      <c r="M83" t="inlineStr"/>
-      <c r="N83" t="inlineStr"/>
       <c r="O83" t="n">
         <v>2</v>
       </c>
@@ -3903,15 +3370,9 @@
       <c r="A85" t="n">
         <v>41</v>
       </c>
-      <c r="B85" t="inlineStr">
-        <is>
-          <t>26_10477</t>
-        </is>
-      </c>
       <c r="C85" t="n">
         <v>30.43</v>
       </c>
-      <c r="D85" t="inlineStr"/>
       <c r="E85" t="n">
         <v>20.5</v>
       </c>
@@ -3921,13 +3382,6 @@
       <c r="G85" t="n">
         <v>21</v>
       </c>
-      <c r="H85" t="inlineStr"/>
-      <c r="I85" t="inlineStr"/>
-      <c r="J85" t="inlineStr"/>
-      <c r="K85" t="inlineStr"/>
-      <c r="L85" t="inlineStr"/>
-      <c r="M85" t="inlineStr"/>
-      <c r="N85" t="inlineStr"/>
       <c r="O85" t="n">
         <v>2</v>
       </c>
@@ -3985,15 +3439,9 @@
       <c r="A87" t="n">
         <v>42</v>
       </c>
-      <c r="B87" t="inlineStr">
-        <is>
-          <t>26_10478</t>
-        </is>
-      </c>
       <c r="C87" t="n">
         <v>30.04</v>
       </c>
-      <c r="D87" t="inlineStr"/>
       <c r="E87" t="n">
         <v>20.5</v>
       </c>
@@ -4003,13 +3451,6 @@
       <c r="G87" t="n">
         <v>21</v>
       </c>
-      <c r="H87" t="inlineStr"/>
-      <c r="I87" t="inlineStr"/>
-      <c r="J87" t="inlineStr"/>
-      <c r="K87" t="inlineStr"/>
-      <c r="L87" t="inlineStr"/>
-      <c r="M87" t="inlineStr"/>
-      <c r="N87" t="inlineStr"/>
       <c r="O87" t="n">
         <v>2</v>
       </c>
@@ -4067,15 +3508,9 @@
       <c r="A89" t="n">
         <v>43</v>
       </c>
-      <c r="B89" t="inlineStr">
-        <is>
-          <t>26_10479</t>
-        </is>
-      </c>
       <c r="C89" t="n">
         <v>30.78</v>
       </c>
-      <c r="D89" t="inlineStr"/>
       <c r="E89" t="n">
         <v>20.5</v>
       </c>
@@ -4085,13 +3520,6 @@
       <c r="G89" t="n">
         <v>21</v>
       </c>
-      <c r="H89" t="inlineStr"/>
-      <c r="I89" t="inlineStr"/>
-      <c r="J89" t="inlineStr"/>
-      <c r="K89" t="inlineStr"/>
-      <c r="L89" t="inlineStr"/>
-      <c r="M89" t="inlineStr"/>
-      <c r="N89" t="inlineStr"/>
       <c r="O89" t="n">
         <v>2</v>
       </c>
@@ -4149,15 +3577,9 @@
       <c r="A91" t="n">
         <v>44</v>
       </c>
-      <c r="B91" t="inlineStr">
-        <is>
-          <t>26_10480</t>
-        </is>
-      </c>
       <c r="C91" t="n">
         <v>30.72</v>
       </c>
-      <c r="D91" t="inlineStr"/>
       <c r="E91" t="n">
         <v>20.5</v>
       </c>
@@ -4167,13 +3589,6 @@
       <c r="G91" t="n">
         <v>21</v>
       </c>
-      <c r="H91" t="inlineStr"/>
-      <c r="I91" t="inlineStr"/>
-      <c r="J91" t="inlineStr"/>
-      <c r="K91" t="inlineStr"/>
-      <c r="L91" t="inlineStr"/>
-      <c r="M91" t="inlineStr"/>
-      <c r="N91" t="inlineStr"/>
       <c r="O91" t="n">
         <v>2</v>
       </c>
@@ -4231,15 +3646,9 @@
       <c r="A93" t="n">
         <v>45</v>
       </c>
-      <c r="B93" t="inlineStr">
-        <is>
-          <t>26_10481</t>
-        </is>
-      </c>
       <c r="C93" t="n">
         <v>30.41</v>
       </c>
-      <c r="D93" t="inlineStr"/>
       <c r="E93" t="n">
         <v>20.5</v>
       </c>
@@ -4249,13 +3658,6 @@
       <c r="G93" t="n">
         <v>21</v>
       </c>
-      <c r="H93" t="inlineStr"/>
-      <c r="I93" t="inlineStr"/>
-      <c r="J93" t="inlineStr"/>
-      <c r="K93" t="inlineStr"/>
-      <c r="L93" t="inlineStr"/>
-      <c r="M93" t="inlineStr"/>
-      <c r="N93" t="inlineStr"/>
       <c r="O93" t="n">
         <v>2</v>
       </c>
@@ -4313,15 +3715,9 @@
       <c r="A95" t="n">
         <v>46</v>
       </c>
-      <c r="B95" t="inlineStr">
-        <is>
-          <t>26_10482</t>
-        </is>
-      </c>
       <c r="C95" t="n">
         <v>31.35</v>
       </c>
-      <c r="D95" t="inlineStr"/>
       <c r="E95" t="n">
         <v>20.5</v>
       </c>
@@ -4331,13 +3727,6 @@
       <c r="G95" t="n">
         <v>21</v>
       </c>
-      <c r="H95" t="inlineStr"/>
-      <c r="I95" t="inlineStr"/>
-      <c r="J95" t="inlineStr"/>
-      <c r="K95" t="inlineStr"/>
-      <c r="L95" t="inlineStr"/>
-      <c r="M95" t="inlineStr"/>
-      <c r="N95" t="inlineStr"/>
       <c r="O95" t="n">
         <v>2</v>
       </c>
@@ -4395,15 +3784,9 @@
       <c r="A97" t="n">
         <v>47</v>
       </c>
-      <c r="B97" t="inlineStr">
-        <is>
-          <t>26_10483</t>
-        </is>
-      </c>
       <c r="C97" t="n">
         <v>30.11</v>
       </c>
-      <c r="D97" t="inlineStr"/>
       <c r="E97" t="n">
         <v>20.5</v>
       </c>
@@ -4413,13 +3796,6 @@
       <c r="G97" t="n">
         <v>21</v>
       </c>
-      <c r="H97" t="inlineStr"/>
-      <c r="I97" t="inlineStr"/>
-      <c r="J97" t="inlineStr"/>
-      <c r="K97" t="inlineStr"/>
-      <c r="L97" t="inlineStr"/>
-      <c r="M97" t="inlineStr"/>
-      <c r="N97" t="inlineStr"/>
       <c r="O97" t="n">
         <v>2</v>
       </c>
@@ -4477,15 +3853,9 @@
       <c r="A99" t="n">
         <v>48</v>
       </c>
-      <c r="B99" t="inlineStr">
-        <is>
-          <t>26_10484</t>
-        </is>
-      </c>
       <c r="C99" t="n">
         <v>30.24</v>
       </c>
-      <c r="D99" t="inlineStr"/>
       <c r="E99" t="n">
         <v>20.5</v>
       </c>
@@ -4495,13 +3865,6 @@
       <c r="G99" t="n">
         <v>21</v>
       </c>
-      <c r="H99" t="inlineStr"/>
-      <c r="I99" t="inlineStr"/>
-      <c r="J99" t="inlineStr"/>
-      <c r="K99" t="inlineStr"/>
-      <c r="L99" t="inlineStr"/>
-      <c r="M99" t="inlineStr"/>
-      <c r="N99" t="inlineStr"/>
       <c r="O99" t="n">
         <v>2</v>
       </c>
@@ -4559,15 +3922,9 @@
       <c r="A101" t="n">
         <v>49</v>
       </c>
-      <c r="B101" t="inlineStr">
-        <is>
-          <t>26_10485</t>
-        </is>
-      </c>
       <c r="C101" t="n">
         <v>30.42</v>
       </c>
-      <c r="D101" t="inlineStr"/>
       <c r="E101" t="n">
         <v>20.5</v>
       </c>
@@ -4577,13 +3934,6 @@
       <c r="G101" t="n">
         <v>21</v>
       </c>
-      <c r="H101" t="inlineStr"/>
-      <c r="I101" t="inlineStr"/>
-      <c r="J101" t="inlineStr"/>
-      <c r="K101" t="inlineStr"/>
-      <c r="L101" t="inlineStr"/>
-      <c r="M101" t="inlineStr"/>
-      <c r="N101" t="inlineStr"/>
       <c r="O101" t="n">
         <v>2</v>
       </c>
@@ -4641,15 +3991,9 @@
       <c r="A103" t="n">
         <v>50</v>
       </c>
-      <c r="B103" t="inlineStr">
-        <is>
-          <t>26_10486</t>
-        </is>
-      </c>
       <c r="C103" t="n">
         <v>30.32</v>
       </c>
-      <c r="D103" t="inlineStr"/>
       <c r="E103" t="n">
         <v>20.5</v>
       </c>
@@ -4659,13 +4003,6 @@
       <c r="G103" t="n">
         <v>21</v>
       </c>
-      <c r="H103" t="inlineStr"/>
-      <c r="I103" t="inlineStr"/>
-      <c r="J103" t="inlineStr"/>
-      <c r="K103" t="inlineStr"/>
-      <c r="L103" t="inlineStr"/>
-      <c r="M103" t="inlineStr"/>
-      <c r="N103" t="inlineStr"/>
       <c r="O103" t="n">
         <v>2</v>
       </c>
@@ -4723,15 +4060,9 @@
       <c r="A105" t="n">
         <v>51</v>
       </c>
-      <c r="B105" t="inlineStr">
-        <is>
-          <t>26_10487</t>
-        </is>
-      </c>
       <c r="C105" t="n">
         <v>30.39</v>
       </c>
-      <c r="D105" t="inlineStr"/>
       <c r="E105" t="n">
         <v>20.5</v>
       </c>
@@ -4741,13 +4072,6 @@
       <c r="G105" t="n">
         <v>21</v>
       </c>
-      <c r="H105" t="inlineStr"/>
-      <c r="I105" t="inlineStr"/>
-      <c r="J105" t="inlineStr"/>
-      <c r="K105" t="inlineStr"/>
-      <c r="L105" t="inlineStr"/>
-      <c r="M105" t="inlineStr"/>
-      <c r="N105" t="inlineStr"/>
       <c r="O105" t="n">
         <v>2</v>
       </c>
@@ -4805,15 +4129,9 @@
       <c r="A107" t="n">
         <v>52</v>
       </c>
-      <c r="B107" t="inlineStr">
-        <is>
-          <t>26_10488</t>
-        </is>
-      </c>
       <c r="C107" t="n">
         <v>30.47</v>
       </c>
-      <c r="D107" t="inlineStr"/>
       <c r="E107" t="n">
         <v>20.5</v>
       </c>
@@ -4823,13 +4141,6 @@
       <c r="G107" t="n">
         <v>21</v>
       </c>
-      <c r="H107" t="inlineStr"/>
-      <c r="I107" t="inlineStr"/>
-      <c r="J107" t="inlineStr"/>
-      <c r="K107" t="inlineStr"/>
-      <c r="L107" t="inlineStr"/>
-      <c r="M107" t="inlineStr"/>
-      <c r="N107" t="inlineStr"/>
       <c r="O107" t="n">
         <v>2</v>
       </c>
@@ -4887,15 +4198,9 @@
       <c r="A109" t="n">
         <v>53</v>
       </c>
-      <c r="B109" t="inlineStr">
-        <is>
-          <t>26_10489</t>
-        </is>
-      </c>
       <c r="C109" t="n">
         <v>30.66</v>
       </c>
-      <c r="D109" t="inlineStr"/>
       <c r="E109" t="n">
         <v>20.5</v>
       </c>
@@ -4905,13 +4210,6 @@
       <c r="G109" t="n">
         <v>21</v>
       </c>
-      <c r="H109" t="inlineStr"/>
-      <c r="I109" t="inlineStr"/>
-      <c r="J109" t="inlineStr"/>
-      <c r="K109" t="inlineStr"/>
-      <c r="L109" t="inlineStr"/>
-      <c r="M109" t="inlineStr"/>
-      <c r="N109" t="inlineStr"/>
       <c r="O109" t="n">
         <v>2</v>
       </c>
@@ -4969,15 +4267,9 @@
       <c r="A111" t="n">
         <v>54</v>
       </c>
-      <c r="B111" t="inlineStr">
-        <is>
-          <t>26_10490</t>
-        </is>
-      </c>
       <c r="C111" t="n">
         <v>30.38</v>
       </c>
-      <c r="D111" t="inlineStr"/>
       <c r="E111" t="n">
         <v>20.5</v>
       </c>
@@ -4987,13 +4279,6 @@
       <c r="G111" t="n">
         <v>21</v>
       </c>
-      <c r="H111" t="inlineStr"/>
-      <c r="I111" t="inlineStr"/>
-      <c r="J111" t="inlineStr"/>
-      <c r="K111" t="inlineStr"/>
-      <c r="L111" t="inlineStr"/>
-      <c r="M111" t="inlineStr"/>
-      <c r="N111" t="inlineStr"/>
       <c r="O111" t="n">
         <v>2</v>
       </c>
@@ -5051,15 +4336,9 @@
       <c r="A113" t="n">
         <v>55</v>
       </c>
-      <c r="B113" t="inlineStr">
-        <is>
-          <t>26_10491</t>
-        </is>
-      </c>
       <c r="C113" t="n">
         <v>30.21</v>
       </c>
-      <c r="D113" t="inlineStr"/>
       <c r="E113" t="n">
         <v>20.5</v>
       </c>
@@ -5069,13 +4348,6 @@
       <c r="G113" t="n">
         <v>21</v>
       </c>
-      <c r="H113" t="inlineStr"/>
-      <c r="I113" t="inlineStr"/>
-      <c r="J113" t="inlineStr"/>
-      <c r="K113" t="inlineStr"/>
-      <c r="L113" t="inlineStr"/>
-      <c r="M113" t="inlineStr"/>
-      <c r="N113" t="inlineStr"/>
       <c r="O113" t="n">
         <v>2</v>
       </c>
@@ -5133,15 +4405,9 @@
       <c r="A115" t="n">
         <v>56</v>
       </c>
-      <c r="B115" t="inlineStr">
-        <is>
-          <t>26_10492</t>
-        </is>
-      </c>
       <c r="C115" t="n">
         <v>30.24</v>
       </c>
-      <c r="D115" t="inlineStr"/>
       <c r="E115" t="n">
         <v>20.5</v>
       </c>
@@ -5151,13 +4417,6 @@
       <c r="G115" t="n">
         <v>21</v>
       </c>
-      <c r="H115" t="inlineStr"/>
-      <c r="I115" t="inlineStr"/>
-      <c r="J115" t="inlineStr"/>
-      <c r="K115" t="inlineStr"/>
-      <c r="L115" t="inlineStr"/>
-      <c r="M115" t="inlineStr"/>
-      <c r="N115" t="inlineStr"/>
       <c r="O115" t="n">
         <v>2</v>
       </c>
@@ -5215,15 +4474,9 @@
       <c r="A117" t="n">
         <v>57</v>
       </c>
-      <c r="B117" t="inlineStr">
-        <is>
-          <t>26_10493</t>
-        </is>
-      </c>
       <c r="C117" t="n">
         <v>30.12</v>
       </c>
-      <c r="D117" t="inlineStr"/>
       <c r="E117" t="n">
         <v>20.5</v>
       </c>
@@ -5233,13 +4486,6 @@
       <c r="G117" t="n">
         <v>21</v>
       </c>
-      <c r="H117" t="inlineStr"/>
-      <c r="I117" t="inlineStr"/>
-      <c r="J117" t="inlineStr"/>
-      <c r="K117" t="inlineStr"/>
-      <c r="L117" t="inlineStr"/>
-      <c r="M117" t="inlineStr"/>
-      <c r="N117" t="inlineStr"/>
       <c r="O117" t="n">
         <v>2</v>
       </c>
@@ -5297,15 +4543,9 @@
       <c r="A119" t="n">
         <v>58</v>
       </c>
-      <c r="B119" t="inlineStr">
-        <is>
-          <t>26_10494</t>
-        </is>
-      </c>
       <c r="C119" t="n">
         <v>30.51</v>
       </c>
-      <c r="D119" t="inlineStr"/>
       <c r="E119" t="n">
         <v>20.5</v>
       </c>
@@ -5315,13 +4555,6 @@
       <c r="G119" t="n">
         <v>21</v>
       </c>
-      <c r="H119" t="inlineStr"/>
-      <c r="I119" t="inlineStr"/>
-      <c r="J119" t="inlineStr"/>
-      <c r="K119" t="inlineStr"/>
-      <c r="L119" t="inlineStr"/>
-      <c r="M119" t="inlineStr"/>
-      <c r="N119" t="inlineStr"/>
       <c r="O119" t="n">
         <v>2</v>
       </c>
@@ -5379,15 +4612,9 @@
       <c r="A121" t="n">
         <v>59</v>
       </c>
-      <c r="B121" t="inlineStr">
-        <is>
-          <t>26_10495</t>
-        </is>
-      </c>
       <c r="C121" t="n">
         <v>30.14</v>
       </c>
-      <c r="D121" t="inlineStr"/>
       <c r="E121" t="n">
         <v>20.5</v>
       </c>
@@ -5397,13 +4624,6 @@
       <c r="G121" t="n">
         <v>21</v>
       </c>
-      <c r="H121" t="inlineStr"/>
-      <c r="I121" t="inlineStr"/>
-      <c r="J121" t="inlineStr"/>
-      <c r="K121" t="inlineStr"/>
-      <c r="L121" t="inlineStr"/>
-      <c r="M121" t="inlineStr"/>
-      <c r="N121" t="inlineStr"/>
       <c r="O121" t="n">
         <v>2</v>
       </c>
@@ -5461,15 +4681,9 @@
       <c r="A123" t="n">
         <v>60</v>
       </c>
-      <c r="B123" t="inlineStr">
-        <is>
-          <t>26_10496</t>
-        </is>
-      </c>
       <c r="C123" t="n">
         <v>30.17</v>
       </c>
-      <c r="D123" t="inlineStr"/>
       <c r="E123" t="n">
         <v>20.5</v>
       </c>
@@ -5479,13 +4693,6 @@
       <c r="G123" t="n">
         <v>21</v>
       </c>
-      <c r="H123" t="inlineStr"/>
-      <c r="I123" t="inlineStr"/>
-      <c r="J123" t="inlineStr"/>
-      <c r="K123" t="inlineStr"/>
-      <c r="L123" t="inlineStr"/>
-      <c r="M123" t="inlineStr"/>
-      <c r="N123" t="inlineStr"/>
       <c r="O123" t="n">
         <v>2</v>
       </c>
@@ -5543,15 +4750,9 @@
       <c r="A125" t="n">
         <v>61</v>
       </c>
-      <c r="B125" t="inlineStr">
-        <is>
-          <t>26_10497</t>
-        </is>
-      </c>
       <c r="C125" t="n">
         <v>30.2</v>
       </c>
-      <c r="D125" t="inlineStr"/>
       <c r="E125" t="n">
         <v>20.5</v>
       </c>
@@ -5561,13 +4762,6 @@
       <c r="G125" t="n">
         <v>21</v>
       </c>
-      <c r="H125" t="inlineStr"/>
-      <c r="I125" t="inlineStr"/>
-      <c r="J125" t="inlineStr"/>
-      <c r="K125" t="inlineStr"/>
-      <c r="L125" t="inlineStr"/>
-      <c r="M125" t="inlineStr"/>
-      <c r="N125" t="inlineStr"/>
       <c r="O125" t="n">
         <v>2</v>
       </c>
@@ -5625,15 +4819,9 @@
       <c r="A127" t="n">
         <v>62</v>
       </c>
-      <c r="B127" t="inlineStr">
-        <is>
-          <t>26_10498</t>
-        </is>
-      </c>
       <c r="C127" t="n">
         <v>30.2</v>
       </c>
-      <c r="D127" t="inlineStr"/>
       <c r="E127" t="n">
         <v>20.5</v>
       </c>
@@ -5643,13 +4831,6 @@
       <c r="G127" t="n">
         <v>21</v>
       </c>
-      <c r="H127" t="inlineStr"/>
-      <c r="I127" t="inlineStr"/>
-      <c r="J127" t="inlineStr"/>
-      <c r="K127" t="inlineStr"/>
-      <c r="L127" t="inlineStr"/>
-      <c r="M127" t="inlineStr"/>
-      <c r="N127" t="inlineStr"/>
       <c r="O127" t="n">
         <v>2</v>
       </c>
@@ -5707,15 +4888,9 @@
       <c r="A129" t="n">
         <v>63</v>
       </c>
-      <c r="B129" t="inlineStr">
-        <is>
-          <t>26_10499</t>
-        </is>
-      </c>
       <c r="C129" t="n">
         <v>30.06</v>
       </c>
-      <c r="D129" t="inlineStr"/>
       <c r="E129" t="n">
         <v>20.5</v>
       </c>
@@ -5725,18 +4900,589 @@
       <c r="G129" t="n">
         <v>21</v>
       </c>
-      <c r="H129" t="inlineStr"/>
-      <c r="I129" t="inlineStr"/>
-      <c r="J129" t="inlineStr"/>
-      <c r="K129" t="inlineStr"/>
-      <c r="L129" t="inlineStr"/>
-      <c r="M129" t="inlineStr"/>
-      <c r="N129" t="inlineStr"/>
       <c r="O129" t="n">
         <v>2</v>
       </c>
     </row>
   </sheetData>
+  <mergeCells count="576">
+    <mergeCell ref="I32:I33"/>
+    <mergeCell ref="K32:K33"/>
+    <mergeCell ref="K88:K89"/>
+    <mergeCell ref="J60:J61"/>
+    <mergeCell ref="K26:K27"/>
+    <mergeCell ref="M88:M89"/>
+    <mergeCell ref="N22:N23"/>
+    <mergeCell ref="H102:H103"/>
+    <mergeCell ref="M98:M99"/>
+    <mergeCell ref="J102:J103"/>
+    <mergeCell ref="B42:B43"/>
+    <mergeCell ref="M54:M55"/>
+    <mergeCell ref="M90:M91"/>
+    <mergeCell ref="J68:J69"/>
+    <mergeCell ref="D16:D17"/>
+    <mergeCell ref="B6:B7"/>
+    <mergeCell ref="D62:D63"/>
+    <mergeCell ref="I58:I59"/>
+    <mergeCell ref="K58:K59"/>
+    <mergeCell ref="N48:N49"/>
+    <mergeCell ref="K52:K53"/>
+    <mergeCell ref="D18:D19"/>
+    <mergeCell ref="B64:B65"/>
+    <mergeCell ref="D64:D65"/>
+    <mergeCell ref="H28:H29"/>
+    <mergeCell ref="I60:I61"/>
+    <mergeCell ref="M18:M19"/>
+    <mergeCell ref="K116:K117"/>
+    <mergeCell ref="H120:H121"/>
+    <mergeCell ref="M116:M117"/>
+    <mergeCell ref="H92:H93"/>
+    <mergeCell ref="H30:H31"/>
+    <mergeCell ref="H8:H9"/>
+    <mergeCell ref="K118:K119"/>
+    <mergeCell ref="J8:J9"/>
+    <mergeCell ref="M118:M119"/>
+    <mergeCell ref="M96:M97"/>
+    <mergeCell ref="B26:B27"/>
+    <mergeCell ref="H10:H11"/>
+    <mergeCell ref="J10:J11"/>
+    <mergeCell ref="L66:L67"/>
+    <mergeCell ref="I70:I71"/>
+    <mergeCell ref="N66:N67"/>
+    <mergeCell ref="B90:B91"/>
+    <mergeCell ref="J74:J75"/>
+    <mergeCell ref="L68:L69"/>
+    <mergeCell ref="N68:N69"/>
+    <mergeCell ref="L18:L19"/>
+    <mergeCell ref="K46:K47"/>
+    <mergeCell ref="K40:K41"/>
+    <mergeCell ref="D12:D13"/>
+    <mergeCell ref="H110:H111"/>
+    <mergeCell ref="M40:M41"/>
+    <mergeCell ref="K2:K3"/>
+    <mergeCell ref="B44:B45"/>
+    <mergeCell ref="M24:M25"/>
+    <mergeCell ref="I48:I49"/>
+    <mergeCell ref="K48:K49"/>
+    <mergeCell ref="M104:M105"/>
+    <mergeCell ref="K66:K67"/>
+    <mergeCell ref="B108:B109"/>
+    <mergeCell ref="M66:M67"/>
+    <mergeCell ref="M106:M107"/>
+    <mergeCell ref="B32:B33"/>
+    <mergeCell ref="D88:D89"/>
+    <mergeCell ref="D26:D27"/>
+    <mergeCell ref="I124:I125"/>
+    <mergeCell ref="N54:N55"/>
+    <mergeCell ref="J92:J93"/>
+    <mergeCell ref="K124:K125"/>
+    <mergeCell ref="D90:D91"/>
+    <mergeCell ref="H54:H55"/>
+    <mergeCell ref="L62:L63"/>
+    <mergeCell ref="I126:I127"/>
+    <mergeCell ref="N56:N57"/>
+    <mergeCell ref="N122:N123"/>
+    <mergeCell ref="K126:K127"/>
+    <mergeCell ref="H56:H57"/>
+    <mergeCell ref="D80:D81"/>
+    <mergeCell ref="H58:H59"/>
+    <mergeCell ref="N120:N121"/>
+    <mergeCell ref="M46:M47"/>
+    <mergeCell ref="L74:L75"/>
+    <mergeCell ref="J24:J25"/>
+    <mergeCell ref="B98:B99"/>
+    <mergeCell ref="H60:H61"/>
+    <mergeCell ref="M12:M13"/>
+    <mergeCell ref="L76:L77"/>
+    <mergeCell ref="J26:J27"/>
+    <mergeCell ref="H124:H125"/>
+    <mergeCell ref="L26:L27"/>
+    <mergeCell ref="J124:J125"/>
+    <mergeCell ref="M14:M15"/>
+    <mergeCell ref="J118:J119"/>
+    <mergeCell ref="I8:I9"/>
+    <mergeCell ref="J18:J19"/>
+    <mergeCell ref="N82:N83"/>
+    <mergeCell ref="K8:K9"/>
+    <mergeCell ref="J90:J91"/>
+    <mergeCell ref="L90:L91"/>
+    <mergeCell ref="B20:B21"/>
+    <mergeCell ref="I94:I95"/>
+    <mergeCell ref="D20:D21"/>
+    <mergeCell ref="D14:D15"/>
+    <mergeCell ref="I10:I11"/>
+    <mergeCell ref="K10:K11"/>
+    <mergeCell ref="B22:B23"/>
+    <mergeCell ref="H42:H43"/>
+    <mergeCell ref="I74:I75"/>
+    <mergeCell ref="M38:M39"/>
+    <mergeCell ref="J42:J43"/>
+    <mergeCell ref="K74:K75"/>
+    <mergeCell ref="N4:N5"/>
+    <mergeCell ref="H78:H79"/>
+    <mergeCell ref="K68:K69"/>
+    <mergeCell ref="M68:M69"/>
+    <mergeCell ref="N110:N111"/>
+    <mergeCell ref="K18:K19"/>
+    <mergeCell ref="H44:H45"/>
+    <mergeCell ref="I76:I77"/>
+    <mergeCell ref="J44:J45"/>
+    <mergeCell ref="K76:K77"/>
+    <mergeCell ref="B96:B97"/>
+    <mergeCell ref="D96:D97"/>
+    <mergeCell ref="H6:H7"/>
+    <mergeCell ref="B46:B47"/>
+    <mergeCell ref="J6:J7"/>
+    <mergeCell ref="H108:H109"/>
+    <mergeCell ref="D46:D47"/>
+    <mergeCell ref="N62:N63"/>
+    <mergeCell ref="B38:B39"/>
+    <mergeCell ref="L24:L25"/>
+    <mergeCell ref="I28:I29"/>
+    <mergeCell ref="B48:B49"/>
+    <mergeCell ref="D48:D49"/>
+    <mergeCell ref="D104:D105"/>
+    <mergeCell ref="L64:L65"/>
+    <mergeCell ref="D4:D5"/>
+    <mergeCell ref="N64:N65"/>
+    <mergeCell ref="L88:L89"/>
+    <mergeCell ref="I92:I93"/>
+    <mergeCell ref="L128:L129"/>
+    <mergeCell ref="D106:D107"/>
+    <mergeCell ref="N128:N129"/>
+    <mergeCell ref="H32:H33"/>
+    <mergeCell ref="J96:J97"/>
+    <mergeCell ref="K62:K63"/>
+    <mergeCell ref="M62:M63"/>
+    <mergeCell ref="H126:H127"/>
+    <mergeCell ref="M56:M57"/>
+    <mergeCell ref="M122:M123"/>
+    <mergeCell ref="J126:J127"/>
+    <mergeCell ref="B66:B67"/>
+    <mergeCell ref="K64:K65"/>
+    <mergeCell ref="L98:L99"/>
+    <mergeCell ref="M64:M65"/>
+    <mergeCell ref="D84:D85"/>
+    <mergeCell ref="D22:D23"/>
+    <mergeCell ref="B86:B87"/>
+    <mergeCell ref="L12:L13"/>
+    <mergeCell ref="D86:D87"/>
+    <mergeCell ref="H50:H51"/>
+    <mergeCell ref="I16:I17"/>
+    <mergeCell ref="N12:N13"/>
+    <mergeCell ref="D36:D37"/>
+    <mergeCell ref="I26:I27"/>
+    <mergeCell ref="L14:L15"/>
+    <mergeCell ref="H52:H53"/>
+    <mergeCell ref="I18:I19"/>
+    <mergeCell ref="N14:N15"/>
+    <mergeCell ref="J108:J109"/>
+    <mergeCell ref="K90:K91"/>
+    <mergeCell ref="H94:H95"/>
+    <mergeCell ref="K82:K83"/>
+    <mergeCell ref="J32:J33"/>
+    <mergeCell ref="B112:B113"/>
+    <mergeCell ref="L38:L39"/>
+    <mergeCell ref="D112:D113"/>
+    <mergeCell ref="I42:I43"/>
+    <mergeCell ref="N38:N39"/>
+    <mergeCell ref="K42:K43"/>
+    <mergeCell ref="L96:L97"/>
+    <mergeCell ref="J22:J23"/>
+    <mergeCell ref="N90:N91"/>
+    <mergeCell ref="B54:B55"/>
+    <mergeCell ref="B114:B115"/>
+    <mergeCell ref="D54:D55"/>
+    <mergeCell ref="H76:H77"/>
+    <mergeCell ref="D114:D115"/>
+    <mergeCell ref="I44:I45"/>
+    <mergeCell ref="I50:I51"/>
+    <mergeCell ref="J76:J77"/>
+    <mergeCell ref="L40:L41"/>
+    <mergeCell ref="N40:N41"/>
+    <mergeCell ref="H122:H123"/>
+    <mergeCell ref="L80:L81"/>
+    <mergeCell ref="N80:N81"/>
+    <mergeCell ref="B56:B57"/>
+    <mergeCell ref="I6:I7"/>
+    <mergeCell ref="K6:K7"/>
+    <mergeCell ref="I108:I109"/>
+    <mergeCell ref="D34:D35"/>
+    <mergeCell ref="K108:K109"/>
+    <mergeCell ref="M34:M35"/>
+    <mergeCell ref="I72:I73"/>
+    <mergeCell ref="N2:N3"/>
+    <mergeCell ref="K72:K73"/>
+    <mergeCell ref="H2:H3"/>
+    <mergeCell ref="M128:M129"/>
+    <mergeCell ref="J20:J21"/>
+    <mergeCell ref="L20:L21"/>
+    <mergeCell ref="I96:I97"/>
+    <mergeCell ref="L84:L85"/>
+    <mergeCell ref="L22:L23"/>
+    <mergeCell ref="N84:N85"/>
+    <mergeCell ref="N78:N79"/>
+    <mergeCell ref="L34:L35"/>
+    <mergeCell ref="I38:I39"/>
+    <mergeCell ref="D102:D103"/>
+    <mergeCell ref="I98:I99"/>
+    <mergeCell ref="N28:N29"/>
+    <mergeCell ref="L86:L87"/>
+    <mergeCell ref="N86:N87"/>
+    <mergeCell ref="N30:N31"/>
+    <mergeCell ref="L46:L47"/>
+    <mergeCell ref="B16:B17"/>
+    <mergeCell ref="N94:N95"/>
+    <mergeCell ref="K20:K21"/>
+    <mergeCell ref="J48:J49"/>
+    <mergeCell ref="M20:M21"/>
+    <mergeCell ref="B122:B123"/>
+    <mergeCell ref="L48:L49"/>
+    <mergeCell ref="B18:B19"/>
+    <mergeCell ref="L112:L113"/>
+    <mergeCell ref="M78:M79"/>
+    <mergeCell ref="I116:I117"/>
+    <mergeCell ref="N112:N113"/>
+    <mergeCell ref="N106:N107"/>
+    <mergeCell ref="B82:B83"/>
+    <mergeCell ref="L114:L115"/>
+    <mergeCell ref="M80:M81"/>
+    <mergeCell ref="I118:I119"/>
+    <mergeCell ref="K96:K97"/>
+    <mergeCell ref="H100:H101"/>
+    <mergeCell ref="H66:H67"/>
+    <mergeCell ref="J66:J67"/>
+    <mergeCell ref="K98:K99"/>
+    <mergeCell ref="H16:H17"/>
+    <mergeCell ref="K4:K5"/>
+    <mergeCell ref="H18:H19"/>
+    <mergeCell ref="B4:B5"/>
+    <mergeCell ref="K16:K17"/>
+    <mergeCell ref="B110:B111"/>
+    <mergeCell ref="L36:L37"/>
+    <mergeCell ref="D110:D111"/>
+    <mergeCell ref="J72:J73"/>
+    <mergeCell ref="N36:N37"/>
+    <mergeCell ref="B72:B73"/>
+    <mergeCell ref="D128:D129"/>
+    <mergeCell ref="I2:I3"/>
+    <mergeCell ref="N100:N101"/>
+    <mergeCell ref="B70:B71"/>
+    <mergeCell ref="D70:D71"/>
+    <mergeCell ref="I66:I67"/>
+    <mergeCell ref="L102:L103"/>
+    <mergeCell ref="N102:N103"/>
+    <mergeCell ref="I22:I23"/>
+    <mergeCell ref="K84:K85"/>
+    <mergeCell ref="K22:K23"/>
+    <mergeCell ref="M84:M85"/>
+    <mergeCell ref="M22:M23"/>
+    <mergeCell ref="B88:B89"/>
+    <mergeCell ref="H98:H99"/>
+    <mergeCell ref="J54:J55"/>
+    <mergeCell ref="K86:K87"/>
+    <mergeCell ref="L54:L55"/>
+    <mergeCell ref="M86:M87"/>
+    <mergeCell ref="J16:J17"/>
+    <mergeCell ref="M36:M37"/>
+    <mergeCell ref="M30:M31"/>
+    <mergeCell ref="J56:J57"/>
+    <mergeCell ref="L56:L57"/>
+    <mergeCell ref="N34:N35"/>
+    <mergeCell ref="K38:K39"/>
+    <mergeCell ref="D58:D59"/>
+    <mergeCell ref="J120:J121"/>
+    <mergeCell ref="L120:L121"/>
+    <mergeCell ref="M4:M5"/>
+    <mergeCell ref="D60:D61"/>
+    <mergeCell ref="K112:K113"/>
+    <mergeCell ref="H116:H117"/>
+    <mergeCell ref="M112:M113"/>
+    <mergeCell ref="D124:D125"/>
+    <mergeCell ref="I54:I55"/>
+    <mergeCell ref="H26:H27"/>
+    <mergeCell ref="H82:H83"/>
+    <mergeCell ref="K54:K55"/>
+    <mergeCell ref="J82:J83"/>
+    <mergeCell ref="K114:K115"/>
+    <mergeCell ref="H118:H119"/>
+    <mergeCell ref="B12:B13"/>
+    <mergeCell ref="M114:M115"/>
+    <mergeCell ref="M70:M71"/>
+    <mergeCell ref="B14:B15"/>
+    <mergeCell ref="J98:J99"/>
+    <mergeCell ref="J4:J5"/>
+    <mergeCell ref="B78:B79"/>
+    <mergeCell ref="L4:L5"/>
+    <mergeCell ref="D78:D79"/>
+    <mergeCell ref="I68:I69"/>
+    <mergeCell ref="B28:B29"/>
+    <mergeCell ref="B80:B81"/>
+    <mergeCell ref="I82:I83"/>
+    <mergeCell ref="D8:D9"/>
+    <mergeCell ref="N24:N25"/>
+    <mergeCell ref="B40:B41"/>
+    <mergeCell ref="H24:H25"/>
+    <mergeCell ref="H48:H49"/>
+    <mergeCell ref="D10:D11"/>
+    <mergeCell ref="M100:M101"/>
+    <mergeCell ref="B104:B105"/>
+    <mergeCell ref="J88:J89"/>
+    <mergeCell ref="L82:L83"/>
+    <mergeCell ref="M102:M103"/>
+    <mergeCell ref="B106:B107"/>
+    <mergeCell ref="H68:H69"/>
+    <mergeCell ref="N50:N51"/>
+    <mergeCell ref="L58:L59"/>
+    <mergeCell ref="I62:I63"/>
+    <mergeCell ref="N58:N59"/>
+    <mergeCell ref="D126:D127"/>
+    <mergeCell ref="I56:I57"/>
+    <mergeCell ref="I122:I123"/>
+    <mergeCell ref="K122:K123"/>
+    <mergeCell ref="K56:K57"/>
+    <mergeCell ref="N52:N53"/>
+    <mergeCell ref="M28:M29"/>
+    <mergeCell ref="N116:N117"/>
+    <mergeCell ref="K120:K121"/>
+    <mergeCell ref="B84:B85"/>
+    <mergeCell ref="M120:M121"/>
+    <mergeCell ref="N118:N119"/>
+    <mergeCell ref="H12:H13"/>
+    <mergeCell ref="M8:M9"/>
+    <mergeCell ref="J12:J13"/>
+    <mergeCell ref="L72:L73"/>
+    <mergeCell ref="B92:B93"/>
+    <mergeCell ref="B30:B31"/>
+    <mergeCell ref="D30:D31"/>
+    <mergeCell ref="H14:H15"/>
+    <mergeCell ref="J114:J115"/>
+    <mergeCell ref="J14:J15"/>
+    <mergeCell ref="L70:L71"/>
+    <mergeCell ref="N70:N71"/>
+    <mergeCell ref="B94:B95"/>
+    <mergeCell ref="M52:M53"/>
+    <mergeCell ref="D94:D95"/>
+    <mergeCell ref="H38:H39"/>
+    <mergeCell ref="J38:J39"/>
+    <mergeCell ref="H74:H75"/>
+    <mergeCell ref="N46:N47"/>
+    <mergeCell ref="K110:K111"/>
+    <mergeCell ref="M110:M111"/>
+    <mergeCell ref="D76:D77"/>
+    <mergeCell ref="H40:H41"/>
+    <mergeCell ref="J40:J41"/>
+    <mergeCell ref="J104:J105"/>
+    <mergeCell ref="K70:K71"/>
+    <mergeCell ref="L104:L105"/>
+    <mergeCell ref="B34:B35"/>
+    <mergeCell ref="D28:D29"/>
+    <mergeCell ref="I24:I25"/>
+    <mergeCell ref="M32:M33"/>
+    <mergeCell ref="L60:L61"/>
+    <mergeCell ref="N60:N61"/>
+    <mergeCell ref="B36:B37"/>
+    <mergeCell ref="D92:D93"/>
+    <mergeCell ref="I88:I89"/>
+    <mergeCell ref="D42:D43"/>
+    <mergeCell ref="L124:L125"/>
+    <mergeCell ref="I128:I129"/>
+    <mergeCell ref="N124:N125"/>
+    <mergeCell ref="K128:K129"/>
+    <mergeCell ref="I90:I91"/>
+    <mergeCell ref="J110:J111"/>
+    <mergeCell ref="N126:N127"/>
+    <mergeCell ref="H20:H21"/>
+    <mergeCell ref="I80:I81"/>
+    <mergeCell ref="D6:D7"/>
+    <mergeCell ref="B100:B101"/>
+    <mergeCell ref="M58:M59"/>
+    <mergeCell ref="J84:J85"/>
+    <mergeCell ref="B62:B63"/>
+    <mergeCell ref="J122:J123"/>
+    <mergeCell ref="J78:J79"/>
+    <mergeCell ref="L78:L79"/>
+    <mergeCell ref="J28:J29"/>
+    <mergeCell ref="K60:K61"/>
+    <mergeCell ref="B102:B103"/>
+    <mergeCell ref="H64:H65"/>
+    <mergeCell ref="L28:L29"/>
+    <mergeCell ref="M60:M61"/>
+    <mergeCell ref="J86:J87"/>
+    <mergeCell ref="B120:B121"/>
+    <mergeCell ref="D120:D121"/>
+    <mergeCell ref="J30:J31"/>
+    <mergeCell ref="L92:L93"/>
+    <mergeCell ref="L30:L31"/>
+    <mergeCell ref="L8:L9"/>
+    <mergeCell ref="H46:H47"/>
+    <mergeCell ref="I12:I13"/>
+    <mergeCell ref="N8:N9"/>
+    <mergeCell ref="K12:K13"/>
+    <mergeCell ref="B24:B25"/>
+    <mergeCell ref="D24:D25"/>
+    <mergeCell ref="L10:L11"/>
+    <mergeCell ref="I14:I15"/>
+    <mergeCell ref="N10:N11"/>
+    <mergeCell ref="K14:K15"/>
+    <mergeCell ref="I78:I79"/>
+    <mergeCell ref="M42:M43"/>
+    <mergeCell ref="N74:N75"/>
+    <mergeCell ref="K78:K79"/>
+    <mergeCell ref="J106:J107"/>
+    <mergeCell ref="N114:N115"/>
+    <mergeCell ref="M44:M45"/>
+    <mergeCell ref="D100:D101"/>
+    <mergeCell ref="B50:B51"/>
+    <mergeCell ref="L110:L111"/>
+    <mergeCell ref="I46:I47"/>
+    <mergeCell ref="D50:D51"/>
+    <mergeCell ref="I40:I41"/>
+    <mergeCell ref="D44:D45"/>
+    <mergeCell ref="M48:M49"/>
+    <mergeCell ref="B52:B53"/>
+    <mergeCell ref="D52:D53"/>
+    <mergeCell ref="D108:D109"/>
+    <mergeCell ref="I104:I105"/>
+    <mergeCell ref="K104:K105"/>
+    <mergeCell ref="H34:H35"/>
+    <mergeCell ref="I106:I107"/>
+    <mergeCell ref="D32:D33"/>
+    <mergeCell ref="K106:K107"/>
+    <mergeCell ref="H88:H89"/>
+    <mergeCell ref="D72:D73"/>
+    <mergeCell ref="H36:H37"/>
+    <mergeCell ref="J36:J37"/>
+    <mergeCell ref="H72:H73"/>
+    <mergeCell ref="H128:H129"/>
+    <mergeCell ref="M124:M125"/>
+    <mergeCell ref="J128:J129"/>
+    <mergeCell ref="B128:B129"/>
+    <mergeCell ref="H90:H91"/>
+    <mergeCell ref="J100:J101"/>
+    <mergeCell ref="J94:J95"/>
+    <mergeCell ref="L100:L101"/>
+    <mergeCell ref="L94:L95"/>
+    <mergeCell ref="M126:M127"/>
+    <mergeCell ref="I20:I21"/>
+    <mergeCell ref="I84:I85"/>
+    <mergeCell ref="D38:D39"/>
+    <mergeCell ref="D98:D99"/>
+    <mergeCell ref="L16:L17"/>
+    <mergeCell ref="I86:I87"/>
+    <mergeCell ref="M50:M51"/>
+    <mergeCell ref="N16:N17"/>
+    <mergeCell ref="N76:N77"/>
+    <mergeCell ref="K80:K81"/>
+    <mergeCell ref="D40:D41"/>
+    <mergeCell ref="I30:I31"/>
+    <mergeCell ref="K92:K93"/>
+    <mergeCell ref="N26:N27"/>
+    <mergeCell ref="K30:K31"/>
+    <mergeCell ref="N18:N19"/>
+    <mergeCell ref="J34:J35"/>
+    <mergeCell ref="K94:K95"/>
+    <mergeCell ref="B58:B59"/>
+    <mergeCell ref="M94:M95"/>
+    <mergeCell ref="M10:M11"/>
+    <mergeCell ref="N92:N93"/>
+    <mergeCell ref="B60:B61"/>
+    <mergeCell ref="B116:B117"/>
+    <mergeCell ref="H22:H23"/>
+    <mergeCell ref="L42:L43"/>
+    <mergeCell ref="D116:D117"/>
+    <mergeCell ref="I112:I113"/>
+    <mergeCell ref="M74:M75"/>
+    <mergeCell ref="N42:N43"/>
+    <mergeCell ref="B118:B119"/>
+    <mergeCell ref="H80:H81"/>
+    <mergeCell ref="L44:L45"/>
+    <mergeCell ref="D118:D119"/>
+    <mergeCell ref="I114:I115"/>
+    <mergeCell ref="M76:M77"/>
+    <mergeCell ref="N44:N45"/>
+    <mergeCell ref="H96:H97"/>
+    <mergeCell ref="L6:L7"/>
+    <mergeCell ref="N6:N7"/>
+    <mergeCell ref="L108:L109"/>
+    <mergeCell ref="N108:N109"/>
+    <mergeCell ref="I34:I35"/>
+    <mergeCell ref="H62:H63"/>
+    <mergeCell ref="K34:K35"/>
+    <mergeCell ref="J62:J63"/>
+    <mergeCell ref="K28:K29"/>
+    <mergeCell ref="H104:H105"/>
+    <mergeCell ref="H4:H5"/>
+    <mergeCell ref="J64:J65"/>
+    <mergeCell ref="M92:M93"/>
+    <mergeCell ref="N72:N73"/>
+    <mergeCell ref="H106:H107"/>
+    <mergeCell ref="L32:L33"/>
+    <mergeCell ref="I36:I37"/>
+    <mergeCell ref="B8:B9"/>
+    <mergeCell ref="B2:B3"/>
+    <mergeCell ref="D2:D3"/>
+    <mergeCell ref="I100:I101"/>
+    <mergeCell ref="N96:N97"/>
+    <mergeCell ref="K100:K101"/>
+    <mergeCell ref="L126:L127"/>
+    <mergeCell ref="D66:D67"/>
+    <mergeCell ref="N88:N89"/>
+    <mergeCell ref="I102:I103"/>
+    <mergeCell ref="N98:N99"/>
+    <mergeCell ref="K102:K103"/>
+    <mergeCell ref="B68:B69"/>
+    <mergeCell ref="D68:D69"/>
+    <mergeCell ref="H84:H85"/>
+    <mergeCell ref="J50:J51"/>
+    <mergeCell ref="B124:B125"/>
+    <mergeCell ref="H86:H87"/>
+    <mergeCell ref="L50:L51"/>
+    <mergeCell ref="M26:M27"/>
+    <mergeCell ref="J58:J59"/>
+    <mergeCell ref="J52:J53"/>
+    <mergeCell ref="B126:B127"/>
+    <mergeCell ref="L52:L53"/>
+    <mergeCell ref="J116:J117"/>
+    <mergeCell ref="L116:L117"/>
+    <mergeCell ref="M82:M83"/>
+    <mergeCell ref="I120:I121"/>
+    <mergeCell ref="N32:N33"/>
+    <mergeCell ref="K36:K37"/>
+    <mergeCell ref="L118:L119"/>
+    <mergeCell ref="H112:H113"/>
+    <mergeCell ref="J112:J113"/>
+    <mergeCell ref="M2:M3"/>
+    <mergeCell ref="K50:K51"/>
+    <mergeCell ref="K44:K45"/>
+    <mergeCell ref="H114:H115"/>
+    <mergeCell ref="H70:H71"/>
+    <mergeCell ref="J70:J71"/>
+    <mergeCell ref="L122:L123"/>
+    <mergeCell ref="D122:D123"/>
+    <mergeCell ref="D56:D57"/>
+    <mergeCell ref="I52:I53"/>
+    <mergeCell ref="M16:M17"/>
+    <mergeCell ref="M6:M7"/>
+    <mergeCell ref="J80:J81"/>
+    <mergeCell ref="M108:M109"/>
+    <mergeCell ref="B10:B11"/>
+    <mergeCell ref="B74:B75"/>
+    <mergeCell ref="D74:D75"/>
+    <mergeCell ref="I4:I5"/>
+    <mergeCell ref="I64:I65"/>
+    <mergeCell ref="J46:J47"/>
+    <mergeCell ref="M72:M73"/>
+    <mergeCell ref="I110:I111"/>
+    <mergeCell ref="J2:J3"/>
+    <mergeCell ref="B76:B77"/>
+    <mergeCell ref="L2:L3"/>
+    <mergeCell ref="D82:D83"/>
+    <mergeCell ref="N104:N105"/>
+    <mergeCell ref="N20:N21"/>
+    <mergeCell ref="K24:K25"/>
+    <mergeCell ref="L106:L107"/>
+  </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>